--- a/data/trans_dic/P19C07-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C07-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,76</t>
+          <t>1,63; 4,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,08</t>
+          <t>0,98; 3,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,04</t>
+          <t>0,6; 2,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,28</t>
+          <t>1,3; 4,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,67</t>
+          <t>2,4; 4,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,97</t>
+          <t>1,22; 2,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,34</t>
+          <t>1,57; 4,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,84</t>
+          <t>2,06; 3,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,0</t>
+          <t>2,27; 3,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,5</t>
+          <t>1,28; 2,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,17</t>
+          <t>1,35; 3,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,59</t>
+          <t>1,99; 3,49</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,33</t>
+          <t>3,08; 5,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,84</t>
+          <t>2,84; 4,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,65</t>
+          <t>2,79; 4,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,84</t>
+          <t>2,15; 4,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,12</t>
+          <t>3,06; 5,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 5,78</t>
+          <t>3,59; 5,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,98</t>
+          <t>3,18; 4,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,85</t>
+          <t>2,68; 4,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 4,88</t>
+          <t>3,33; 4,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 5,02</t>
+          <t>3,52; 4,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,57</t>
+          <t>3,18; 4,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,41</t>
+          <t>2,79; 4,44</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,85</t>
+          <t>1,68; 5,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,76</t>
+          <t>2,63; 6,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,24</t>
+          <t>0,79; 3,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,78</t>
+          <t>1,98; 4,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,93</t>
+          <t>0,96; 4,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,02</t>
+          <t>2,59; 6,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,12</t>
+          <t>1,7; 5,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 7,45</t>
+          <t>3,8; 7,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,93</t>
+          <t>1,67; 3,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,09</t>
+          <t>3,24; 6,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,62</t>
+          <t>1,52; 3,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,64</t>
+          <t>3,3; 5,45</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 4,23</t>
+          <t>2,73; 4,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,04</t>
+          <t>2,72; 4,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,56</t>
+          <t>2,25; 3,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,13</t>
+          <t>2,35; 4,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,27</t>
+          <t>2,81; 4,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 4,37</t>
+          <t>2,93; 4,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,29</t>
+          <t>2,9; 4,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 4,61</t>
+          <t>3,12; 4,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 4,01</t>
+          <t>2,97; 3,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,99</t>
+          <t>3,04; 4,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 3,7</t>
+          <t>2,8; 3,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,13</t>
+          <t>2,99; 4,15</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10326; 25899</t>
+          <t>11248; 27682</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8173; 24035</t>
+          <t>7624; 23948</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2777; 13885</t>
+          <t>2746; 12889</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6333; 20751</t>
+          <t>6316; 19716</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22512; 44753</t>
+          <t>23003; 44275</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13886; 33523</t>
+          <t>13754; 33262</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10336; 27745</t>
+          <t>10037; 27721</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14623; 27694</t>
+          <t>14846; 28127</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37148; 65989</t>
+          <t>37416; 63419</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23717; 47750</t>
+          <t>24493; 49369</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14863; 34751</t>
+          <t>14755; 35880</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23981; 43339</t>
+          <t>24008; 42147</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40503; 70025</t>
+          <t>40501; 68792</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>49329; 81710</t>
+          <t>47973; 82918</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48000; 78930</t>
+          <t>47405; 79138</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50375; 107851</t>
+          <t>47945; 104902</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41464; 70252</t>
+          <t>42053; 71534</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57788; 91865</t>
+          <t>57067; 91799</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53712; 85018</t>
+          <t>54274; 84890</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>57429; 106643</t>
+          <t>58819; 106270</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>88907; 131059</t>
+          <t>89375; 131544</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>114077; 164521</t>
+          <t>115384; 161481</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>111079; 155465</t>
+          <t>108326; 153151</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>122417; 195494</t>
+          <t>123720; 196530</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7559; 21855</t>
+          <t>7564; 22839</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11699; 29877</t>
+          <t>11612; 30463</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4064; 16172</t>
+          <t>3940; 15296</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12916; 30199</t>
+          <t>12521; 31331</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3923; 16078</t>
+          <t>3930; 16342</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10493; 29763</t>
+          <t>10988; 28371</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8383; 26030</t>
+          <t>8628; 25857</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24617; 48552</t>
+          <t>24746; 46813</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14788; 33770</t>
+          <t>14399; 33272</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27296; 52727</t>
+          <t>28071; 52537</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15418; 36429</t>
+          <t>15276; 35927</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42884; 72367</t>
+          <t>42305; 69935</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>66285; 103953</t>
+          <t>66970; 104631</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>78140; 117505</t>
+          <t>79247; 120723</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59504; 94486</t>
+          <t>59808; 93306</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78659; 138339</t>
+          <t>78577; 139222</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>77527; 117081</t>
+          <t>77052; 115636</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>91399; 137226</t>
+          <t>92021; 134279</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82182; 122565</t>
+          <t>82959; 122879</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>110380; 164804</t>
+          <t>111424; 165652</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>156069; 208510</t>
+          <t>154068; 205090</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>180044; 241733</t>
+          <t>183924; 242637</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>150190; 203983</t>
+          <t>154053; 206240</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>204202; 285533</t>
+          <t>206582; 286812</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C07-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C07-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,02</t>
+          <t>1,47; 3,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,07</t>
+          <t>0,93; 3,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,82</t>
+          <t>0,44; 2,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,07</t>
+          <t>1,13; 3,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,62</t>
+          <t>2,51; 4,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,95</t>
+          <t>1,23; 2,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,34</t>
+          <t>1,62; 4,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,9</t>
+          <t>2,2; 4,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,85</t>
+          <t>2,31; 3,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,59</t>
+          <t>1,27; 2,6</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,27</t>
+          <t>1,41; 3,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,49</t>
+          <t>2,04; 3,54</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,23</t>
+          <t>2,94; 5,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,91</t>
+          <t>2,96; 5,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,66</t>
+          <t>2,8; 4,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,7</t>
+          <t>2,9; 5,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,21</t>
+          <t>3,04; 5,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 5,77</t>
+          <t>3,59; 5,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,97</t>
+          <t>3,05; 4,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 4,84</t>
+          <t>3,53; 5,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 4,89</t>
+          <t>3,33; 4,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 4,93</t>
+          <t>3,53; 4,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,5</t>
+          <t>3,15; 4,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,44</t>
+          <t>3,46; 4,84</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,06</t>
+          <t>1,73; 4,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,89</t>
+          <t>2,72; 6,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,06</t>
+          <t>0,81; 3,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,96</t>
+          <t>1,94; 4,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,0</t>
+          <t>0,88; 3,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,7</t>
+          <t>2,69; 7,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,09</t>
+          <t>1,77; 5,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,18</t>
+          <t>3,63; 6,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,87</t>
+          <t>1,71; 3,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,07</t>
+          <t>3,11; 6,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,57</t>
+          <t>1,53; 3,58</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,45</t>
+          <t>3,09; 5,16</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 4,26</t>
+          <t>2,74; 4,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,15</t>
+          <t>2,73; 4,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,52</t>
+          <t>2,27; 3,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,16</t>
+          <t>2,81; 4,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,22</t>
+          <t>2,85; 4,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 4,27</t>
+          <t>3,0; 4,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 4,3</t>
+          <t>2,87; 4,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,64</t>
+          <t>3,59; 4,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 3,95</t>
+          <t>2,94; 3,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 4,01</t>
+          <t>3,0; 3,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 3,74</t>
+          <t>2,71; 3,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 4,15</t>
+          <t>3,38; 4,41</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11524</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>24047</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31966</t>
+          <t>36110</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11248; 27682</t>
+          <t>10166; 26660</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7624; 23948</t>
+          <t>7213; 23739</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2746; 12889</t>
+          <t>2027; 11944</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6316; 19716</t>
+          <t>6045; 20604</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23003; 44275</t>
+          <t>24050; 44570</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13754; 33262</t>
+          <t>13918; 32872</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10037; 27721</t>
+          <t>10329; 28186</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14846; 28127</t>
+          <t>17244; 32392</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37416; 63419</t>
+          <t>38048; 64723</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24493; 49369</t>
+          <t>24259; 49509</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14755; 35880</t>
+          <t>15455; 35174</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24008; 42147</t>
+          <t>26911; 46848</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74665</t>
+          <t>82799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>83267</t>
+          <t>91684</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>157932</t>
+          <t>174483</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40501; 68792</t>
+          <t>38645; 67894</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47973; 82918</t>
+          <t>49945; 84469</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47405; 79138</t>
+          <t>47582; 78705</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47945; 104902</t>
+          <t>62203; 108749</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42053; 71534</t>
+          <t>41713; 72199</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57067; 91799</t>
+          <t>57112; 92549</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54274; 84890</t>
+          <t>52046; 83559</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58819; 106270</t>
+          <t>74464; 114426</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89375; 131544</t>
+          <t>89482; 128912</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>115384; 161481</t>
+          <t>115825; 163243</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>108326; 153151</t>
+          <t>107245; 151363</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>123720; 196530</t>
+          <t>147116; 206233</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20075</t>
+          <t>21695</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34650</t>
+          <t>36380</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54725</t>
+          <t>58075</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7564; 22839</t>
+          <t>7803; 22210</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11612; 30463</t>
+          <t>12006; 30744</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3940; 15296</t>
+          <t>4062; 16351</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12521; 31331</t>
+          <t>13641; 32542</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3930; 16342</t>
+          <t>3577; 15655</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10988; 28371</t>
+          <t>11386; 29969</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8628; 25857</t>
+          <t>9019; 25735</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24746; 46813</t>
+          <t>26325; 48609</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14399; 33272</t>
+          <t>14697; 32189</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28071; 52537</t>
+          <t>26898; 53110</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15276; 35927</t>
+          <t>15422; 36035</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42305; 69935</t>
+          <t>44104; 73542</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106265</t>
+          <t>116556</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>138358</t>
+          <t>152111</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>244623</t>
+          <t>268667</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>66970; 104631</t>
+          <t>67347; 103332</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79247; 120723</t>
+          <t>79459; 118069</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59808; 93306</t>
+          <t>60165; 94608</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78577; 139222</t>
+          <t>95002; 145880</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>77052; 115636</t>
+          <t>78134; 115038</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>92021; 134279</t>
+          <t>94386; 135399</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82959; 122879</t>
+          <t>81826; 122652</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>111424; 165652</t>
+          <t>129896; 179535</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>154068; 205090</t>
+          <t>152983; 207455</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>183924; 242637</t>
+          <t>181566; 241068</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>154053; 206240</t>
+          <t>149440; 203272</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>206582; 286812</t>
+          <t>237082; 309020</t>
         </is>
       </c>
     </row>
